--- a/data/nzd0053/nzd0053.xlsx
+++ b/data/nzd0053/nzd0053.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O547"/>
+  <dimension ref="A1:O550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28343,6 +28343,159 @@
         <v>392.02</v>
       </c>
       <c r="O547" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>363.07</v>
+      </c>
+      <c r="C548" t="n">
+        <v>351.43</v>
+      </c>
+      <c r="D548" t="n">
+        <v>355.35</v>
+      </c>
+      <c r="E548" t="n">
+        <v>363.67</v>
+      </c>
+      <c r="F548" t="n">
+        <v>366.76</v>
+      </c>
+      <c r="G548" t="n">
+        <v>371.46</v>
+      </c>
+      <c r="H548" t="n">
+        <v>371.24</v>
+      </c>
+      <c r="I548" t="n">
+        <v>371.37</v>
+      </c>
+      <c r="J548" t="n">
+        <v>378.79</v>
+      </c>
+      <c r="K548" t="n">
+        <v>387.45</v>
+      </c>
+      <c r="L548" t="n">
+        <v>388.29</v>
+      </c>
+      <c r="M548" t="n">
+        <v>389.18</v>
+      </c>
+      <c r="N548" t="n">
+        <v>391.22</v>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>363.61</v>
+      </c>
+      <c r="C549" t="n">
+        <v>351.19</v>
+      </c>
+      <c r="D549" t="n">
+        <v>355.65</v>
+      </c>
+      <c r="E549" t="n">
+        <v>363.62</v>
+      </c>
+      <c r="F549" t="n">
+        <v>367</v>
+      </c>
+      <c r="G549" t="n">
+        <v>371.81</v>
+      </c>
+      <c r="H549" t="n">
+        <v>371.34</v>
+      </c>
+      <c r="I549" t="n">
+        <v>371.73</v>
+      </c>
+      <c r="J549" t="n">
+        <v>379.56</v>
+      </c>
+      <c r="K549" t="n">
+        <v>387.44</v>
+      </c>
+      <c r="L549" t="n">
+        <v>388.57</v>
+      </c>
+      <c r="M549" t="n">
+        <v>389.35</v>
+      </c>
+      <c r="N549" t="n">
+        <v>391.59</v>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>363.51</v>
+      </c>
+      <c r="C550" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="D550" t="n">
+        <v>355.24</v>
+      </c>
+      <c r="E550" t="n">
+        <v>363.38</v>
+      </c>
+      <c r="F550" t="n">
+        <v>366.41</v>
+      </c>
+      <c r="G550" t="n">
+        <v>371.36</v>
+      </c>
+      <c r="H550" t="n">
+        <v>370.48</v>
+      </c>
+      <c r="I550" t="n">
+        <v>371.05</v>
+      </c>
+      <c r="J550" t="n">
+        <v>379.41</v>
+      </c>
+      <c r="K550" t="n">
+        <v>386.89</v>
+      </c>
+      <c r="L550" t="n">
+        <v>387.56</v>
+      </c>
+      <c r="M550" t="n">
+        <v>388.69</v>
+      </c>
+      <c r="N550" t="n">
+        <v>390.79</v>
+      </c>
+      <c r="O550" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28359,7 +28512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B564"/>
+  <dimension ref="A1:B567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34002,6 +34155,36 @@
       </c>
       <c r="B564" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>-0.48</v>
       </c>
     </row>
   </sheetData>
@@ -34170,28 +34353,28 @@
         <v>0.0515</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2305130249318656</v>
+        <v>-0.2318313596032697</v>
       </c>
       <c r="J2" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K2" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05192146863826286</v>
+        <v>0.05305901113239331</v>
       </c>
       <c r="M2" t="n">
-        <v>5.474345470182268</v>
+        <v>5.44885121050902</v>
       </c>
       <c r="N2" t="n">
-        <v>54.75446823136905</v>
+        <v>54.46400598538161</v>
       </c>
       <c r="O2" t="n">
-        <v>7.399626222409417</v>
+        <v>7.379973305194377</v>
       </c>
       <c r="P2" t="n">
-        <v>370.7147670489543</v>
+        <v>370.7281983717344</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34248,28 +34431,28 @@
         <v>0.0703</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07418007414924263</v>
+        <v>0.07014376349709789</v>
       </c>
       <c r="J3" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K3" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009321974767073304</v>
+        <v>0.008419971677544158</v>
       </c>
       <c r="M3" t="n">
-        <v>4.737275912108652</v>
+        <v>4.727304370808252</v>
       </c>
       <c r="N3" t="n">
-        <v>33.00125187032121</v>
+        <v>32.90006238315645</v>
       </c>
       <c r="O3" t="n">
-        <v>5.744671606830211</v>
+        <v>5.735857597879889</v>
       </c>
       <c r="P3" t="n">
-        <v>353.1908287215088</v>
+        <v>353.2319527460975</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34326,28 +34509,28 @@
         <v>0.0779</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2321349728575008</v>
+        <v>0.2299854381935646</v>
       </c>
       <c r="J4" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K4" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09996111466083324</v>
+        <v>0.09926086358629094</v>
       </c>
       <c r="M4" t="n">
-        <v>4.13734988325115</v>
+        <v>4.121399526188241</v>
       </c>
       <c r="N4" t="n">
-        <v>27.38057818877394</v>
+        <v>27.25355215619496</v>
       </c>
       <c r="O4" t="n">
-        <v>5.232645429299977</v>
+        <v>5.220493478225499</v>
       </c>
       <c r="P4" t="n">
-        <v>351.348054291374</v>
+        <v>351.3699553419328</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34404,28 +34587,28 @@
         <v>0.1156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2751566985544267</v>
+        <v>0.2747522753269211</v>
       </c>
       <c r="J5" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K5" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1463325154963901</v>
+        <v>0.1474164053576021</v>
       </c>
       <c r="M5" t="n">
-        <v>3.677754950730549</v>
+        <v>3.65927042762142</v>
       </c>
       <c r="N5" t="n">
-        <v>24.92524083079167</v>
+        <v>24.7899244671749</v>
       </c>
       <c r="O5" t="n">
-        <v>4.992518485773656</v>
+        <v>4.978948128588498</v>
       </c>
       <c r="P5" t="n">
-        <v>356.7032704742928</v>
+        <v>356.7073915754204</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34482,28 +34665,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2291758237603278</v>
+        <v>0.2280794509893793</v>
       </c>
       <c r="J6" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K6" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07801524790910008</v>
+        <v>0.07814912814774744</v>
       </c>
       <c r="M6" t="n">
-        <v>4.277031830548655</v>
+        <v>4.258599128629609</v>
       </c>
       <c r="N6" t="n">
-        <v>35.02782164732537</v>
+        <v>34.84257991340658</v>
       </c>
       <c r="O6" t="n">
-        <v>5.918430674370138</v>
+        <v>5.902760363881171</v>
       </c>
       <c r="P6" t="n">
-        <v>361.734812393058</v>
+        <v>361.7459838198998</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34560,28 +34743,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1989048965465915</v>
+        <v>0.1960995492185474</v>
       </c>
       <c r="J7" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K7" t="n">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08272756150138816</v>
+        <v>0.08134591166975447</v>
       </c>
       <c r="M7" t="n">
-        <v>3.803882482942422</v>
+        <v>3.794705715885602</v>
       </c>
       <c r="N7" t="n">
-        <v>24.79738336481439</v>
+        <v>24.70013075166904</v>
       </c>
       <c r="O7" t="n">
-        <v>4.979697115770636</v>
+        <v>4.969922610229363</v>
       </c>
       <c r="P7" t="n">
-        <v>368.9756571052188</v>
+        <v>369.0042212021721</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34638,28 +34821,28 @@
         <v>0.0704</v>
       </c>
       <c r="I8" t="n">
-        <v>0.226934591981556</v>
+        <v>0.2265557081574527</v>
       </c>
       <c r="J8" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K8" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09630163474979869</v>
+        <v>0.09702026407407383</v>
       </c>
       <c r="M8" t="n">
-        <v>3.778054310942846</v>
+        <v>3.758971748803317</v>
       </c>
       <c r="N8" t="n">
-        <v>27.27234744894394</v>
+        <v>27.12482988271015</v>
       </c>
       <c r="O8" t="n">
-        <v>5.222293313185688</v>
+        <v>5.208150332191856</v>
       </c>
       <c r="P8" t="n">
-        <v>365.4053820732072</v>
+        <v>365.4092441673124</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34716,28 +34899,28 @@
         <v>0.0829</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2298162761791326</v>
+        <v>0.2281551782750698</v>
       </c>
       <c r="J9" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K9" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1329281903011253</v>
+        <v>0.1325144139994237</v>
       </c>
       <c r="M9" t="n">
-        <v>3.31681326783866</v>
+        <v>3.307247664168117</v>
       </c>
       <c r="N9" t="n">
-        <v>19.44154714140826</v>
+        <v>19.34912189786915</v>
       </c>
       <c r="O9" t="n">
-        <v>4.409256982917673</v>
+        <v>4.398763678338397</v>
       </c>
       <c r="P9" t="n">
-        <v>366.9134750190601</v>
+        <v>366.9304001659849</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34794,28 +34977,28 @@
         <v>0.0769</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2013166789861505</v>
+        <v>0.199424008175466</v>
       </c>
       <c r="J10" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K10" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1084982809923037</v>
+        <v>0.1077051097533667</v>
       </c>
       <c r="M10" t="n">
-        <v>3.376321515086065</v>
+        <v>3.368924393795306</v>
       </c>
       <c r="N10" t="n">
-        <v>18.79274081820981</v>
+        <v>18.70804618721909</v>
       </c>
       <c r="O10" t="n">
-        <v>4.335059494194954</v>
+        <v>4.325279896979973</v>
       </c>
       <c r="P10" t="n">
-        <v>375.7552478638158</v>
+        <v>375.7745306269188</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34872,28 +35055,28 @@
         <v>0.0823</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1486703647164973</v>
+        <v>0.1489646289970357</v>
       </c>
       <c r="J11" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K11" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07445149186195099</v>
+        <v>0.07552880314216559</v>
       </c>
       <c r="M11" t="n">
-        <v>2.935589391031227</v>
+        <v>2.921366240921261</v>
       </c>
       <c r="N11" t="n">
-        <v>15.50621766506264</v>
+        <v>15.42227894634303</v>
       </c>
       <c r="O11" t="n">
-        <v>3.937793502084974</v>
+        <v>3.927120948779529</v>
       </c>
       <c r="P11" t="n">
-        <v>383.0701777180597</v>
+        <v>383.0671808753935</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34950,28 +35133,28 @@
         <v>0.0887</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1536114358257139</v>
+        <v>0.1559406660816259</v>
       </c>
       <c r="J12" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K12" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06755154489273907</v>
+        <v>0.07013020763924782</v>
       </c>
       <c r="M12" t="n">
-        <v>3.24926634609937</v>
+        <v>3.243594054458201</v>
       </c>
       <c r="N12" t="n">
-        <v>18.38094886935408</v>
+        <v>18.30784547205912</v>
       </c>
       <c r="O12" t="n">
-        <v>4.28730088393083</v>
+        <v>4.278766816742777</v>
       </c>
       <c r="P12" t="n">
-        <v>381.8856369154124</v>
+        <v>381.8619074847882</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35028,28 +35211,28 @@
         <v>0.075</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1741421184343153</v>
+        <v>0.1746929575085385</v>
       </c>
       <c r="J13" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K13" t="n">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07163946521746034</v>
+        <v>0.07283570679535079</v>
       </c>
       <c r="M13" t="n">
-        <v>3.53219814904186</v>
+        <v>3.516237704408835</v>
       </c>
       <c r="N13" t="n">
-        <v>22.21250606287841</v>
+        <v>22.09282100267242</v>
       </c>
       <c r="O13" t="n">
-        <v>4.713014540915231</v>
+        <v>4.700300097086613</v>
       </c>
       <c r="P13" t="n">
-        <v>383.9704446879882</v>
+        <v>383.9648368406802</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35106,28 +35289,28 @@
         <v>0.0617</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2882679773591332</v>
+        <v>0.2883572370828205</v>
       </c>
       <c r="J14" t="n">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K14" t="n">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1726382073238685</v>
+        <v>0.1743891924862702</v>
       </c>
       <c r="M14" t="n">
-        <v>3.51196499434249</v>
+        <v>3.494364035675271</v>
       </c>
       <c r="N14" t="n">
-        <v>22.48147109614804</v>
+        <v>22.35902247903995</v>
       </c>
       <c r="O14" t="n">
-        <v>4.741462970028136</v>
+        <v>4.728532804056662</v>
       </c>
       <c r="P14" t="n">
-        <v>383.5286625290746</v>
+        <v>383.527753987569</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35165,7 +35348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O547"/>
+  <dimension ref="A1:O550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77275,6 +77458,237 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>-35.028783993265435,173.9164196069458</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>-35.029312474849036,173.91578099669402</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>-35.02992491397898,173.9152788194584</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-35.03057305316716,173.91484614896876</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>-35.031237693595166,173.91446296287228</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>-35.03191558460695,173.91415704340562</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>-35.03262966602166,173.91398252635634</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>-35.03335244396538,173.91380529367504</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>-35.03408339903212,173.91366619174633</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>-35.03480458313253,173.91354308782329</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>-35.03552089906462,173.91342770442958</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>-35.03623662938277,173.91332385914146</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>-35.03695837049849,173.91333581266082</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>-35.02878687049237,173.91642438214913</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>-35.029311196073664,173.9157788743745</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>-35.029926470624865,173.9152815088847</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-35.030572824246285,173.91484567679308</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>-35.031238610847794,173.91446534570488</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>-35.031916504207636,173.91416071360757</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>-35.03262983717033,173.91398360263912</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>-35.03335314025589,173.91380914820942</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>-35.03408504047062,173.9136743934282</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>-35.034804566367214,173.91354298011086</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>-35.03552122325916,173.91343074851906</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>-35.03623672763898,173.91332571895117</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>-35.036958390680496,173.91333986878536</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-14 22:17:57+00:00</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>-35.028786337672585,173.9164234978522</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>-35.02931178217904,173.91577984710426</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>-35.029924343208826,173.9152778333354</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-35.03057172542606,173.91484341034982</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>-35.031236355935015,173.91445948790812</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>-35.03191532186389,173.9141559947765</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>-35.032628365291465,173.91397434660735</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>-35.033351825040356,173.9138018674223</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>-35.03408472070992,173.91367279569792</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>-35.034803644275584,173.91353705592707</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>-35.03552005384279,173.91341976805353</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>-35.03623634617354,173.91331849851352</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>-35.03695834704357,173.9133310987864</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0053/nzd0053.xlsx
+++ b/data/nzd0053/nzd0053.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O550"/>
+  <dimension ref="A1:O554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28496,6 +28496,210 @@
         <v>390.79</v>
       </c>
       <c r="O550" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>363.35</v>
+      </c>
+      <c r="C551" t="n">
+        <v>351.72</v>
+      </c>
+      <c r="D551" t="n">
+        <v>355.44</v>
+      </c>
+      <c r="E551" t="n">
+        <v>363.35</v>
+      </c>
+      <c r="F551" t="n">
+        <v>366.13</v>
+      </c>
+      <c r="G551" t="n">
+        <v>370.78</v>
+      </c>
+      <c r="H551" t="n">
+        <v>370.18</v>
+      </c>
+      <c r="I551" t="n">
+        <v>371.03</v>
+      </c>
+      <c r="J551" t="n">
+        <v>379.42</v>
+      </c>
+      <c r="K551" t="n">
+        <v>386.93</v>
+      </c>
+      <c r="L551" t="n">
+        <v>387.91</v>
+      </c>
+      <c r="M551" t="n">
+        <v>388.62</v>
+      </c>
+      <c r="N551" t="n">
+        <v>389.95</v>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>363.53</v>
+      </c>
+      <c r="C552" t="n">
+        <v>351.88</v>
+      </c>
+      <c r="D552" t="n">
+        <v>355.54</v>
+      </c>
+      <c r="E552" t="n">
+        <v>363.43</v>
+      </c>
+      <c r="F552" t="n">
+        <v>366.3</v>
+      </c>
+      <c r="G552" t="n">
+        <v>371.07</v>
+      </c>
+      <c r="H552" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="I552" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="J552" t="n">
+        <v>379.59</v>
+      </c>
+      <c r="K552" t="n">
+        <v>386.97</v>
+      </c>
+      <c r="L552" t="n">
+        <v>387.92</v>
+      </c>
+      <c r="M552" t="n">
+        <v>388.95</v>
+      </c>
+      <c r="N552" t="n">
+        <v>390.14</v>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>363.28</v>
+      </c>
+      <c r="C553" t="n">
+        <v>351.93</v>
+      </c>
+      <c r="D553" t="n">
+        <v>355.97</v>
+      </c>
+      <c r="E553" t="n">
+        <v>363.76</v>
+      </c>
+      <c r="F553" t="n">
+        <v>366.34</v>
+      </c>
+      <c r="G553" t="n">
+        <v>371.24</v>
+      </c>
+      <c r="H553" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="I553" t="n">
+        <v>371</v>
+      </c>
+      <c r="J553" t="n">
+        <v>379.93</v>
+      </c>
+      <c r="K553" t="n">
+        <v>386.93</v>
+      </c>
+      <c r="L553" t="n">
+        <v>388.13</v>
+      </c>
+      <c r="M553" t="n">
+        <v>388.66</v>
+      </c>
+      <c r="N553" t="n">
+        <v>389.33</v>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>364.53</v>
+      </c>
+      <c r="C554" t="n">
+        <v>352.87</v>
+      </c>
+      <c r="D554" t="n">
+        <v>357.19</v>
+      </c>
+      <c r="E554" t="n">
+        <v>364.41</v>
+      </c>
+      <c r="F554" t="n">
+        <v>366.71</v>
+      </c>
+      <c r="G554" t="n">
+        <v>371.48</v>
+      </c>
+      <c r="H554" t="n">
+        <v>369.91</v>
+      </c>
+      <c r="I554" t="n">
+        <v>370.35</v>
+      </c>
+      <c r="J554" t="n">
+        <v>378.77</v>
+      </c>
+      <c r="K554" t="n">
+        <v>387.2</v>
+      </c>
+      <c r="L554" t="n">
+        <v>388.79</v>
+      </c>
+      <c r="M554" t="n">
+        <v>389.31</v>
+      </c>
+      <c r="N554" t="n">
+        <v>388.93</v>
+      </c>
+      <c r="O554" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28512,7 +28716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B567"/>
+  <dimension ref="A1:B571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34185,6 +34389,46 @@
       </c>
       <c r="B567" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -34353,28 +34597,28 @@
         <v>0.0515</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2318313596032697</v>
+        <v>-0.2331223708475704</v>
       </c>
       <c r="J2" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K2" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05305901113239331</v>
+        <v>0.05439702984685468</v>
       </c>
       <c r="M2" t="n">
-        <v>5.44885121050902</v>
+        <v>5.413709105222781</v>
       </c>
       <c r="N2" t="n">
-        <v>54.46400598538161</v>
+        <v>54.07807596943245</v>
       </c>
       <c r="O2" t="n">
-        <v>7.379973305194377</v>
+        <v>7.353779706343701</v>
       </c>
       <c r="P2" t="n">
-        <v>370.7281983717344</v>
+        <v>370.741402457949</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34431,28 +34675,28 @@
         <v>0.0703</v>
       </c>
       <c r="I3" t="n">
-        <v>0.07014376349709789</v>
+        <v>0.06601859430426414</v>
       </c>
       <c r="J3" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K3" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008419971677544158</v>
+        <v>0.00756578479173875</v>
       </c>
       <c r="M3" t="n">
-        <v>4.727304370808252</v>
+        <v>4.709181000262263</v>
       </c>
       <c r="N3" t="n">
-        <v>32.90006238315645</v>
+        <v>32.72653151397753</v>
       </c>
       <c r="O3" t="n">
-        <v>5.735857597879889</v>
+        <v>5.720710752518215</v>
       </c>
       <c r="P3" t="n">
-        <v>353.2319527460975</v>
+        <v>353.2741566431814</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34509,28 +34753,28 @@
         <v>0.0779</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2299854381935646</v>
+        <v>0.2280395929485828</v>
       </c>
       <c r="J4" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K4" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09926086358629094</v>
+        <v>0.09905730088198783</v>
       </c>
       <c r="M4" t="n">
-        <v>4.121399526188241</v>
+        <v>4.097533319781316</v>
       </c>
       <c r="N4" t="n">
-        <v>27.25355215619496</v>
+        <v>27.0739039050782</v>
       </c>
       <c r="O4" t="n">
-        <v>5.220493478225499</v>
+        <v>5.203258969634146</v>
       </c>
       <c r="P4" t="n">
-        <v>351.3699553419328</v>
+        <v>351.3898557347065</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34587,28 +34831,28 @@
         <v>0.1156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2747522753269211</v>
+        <v>0.2744379203732699</v>
       </c>
       <c r="J5" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K5" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1474164053576021</v>
+        <v>0.1490586392179661</v>
       </c>
       <c r="M5" t="n">
-        <v>3.65927042762142</v>
+        <v>3.635627282499834</v>
       </c>
       <c r="N5" t="n">
-        <v>24.7899244671749</v>
+        <v>24.61219851846509</v>
       </c>
       <c r="O5" t="n">
-        <v>4.978948128588498</v>
+        <v>4.961068283995402</v>
       </c>
       <c r="P5" t="n">
-        <v>356.7073915754204</v>
+        <v>356.7106019366969</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34665,28 +34909,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2280794509893793</v>
+        <v>0.2261454645624478</v>
       </c>
       <c r="J6" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K6" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07814912814774744</v>
+        <v>0.0779994321338312</v>
       </c>
       <c r="M6" t="n">
-        <v>4.258599128629609</v>
+        <v>4.236432507267147</v>
       </c>
       <c r="N6" t="n">
-        <v>34.84257991340658</v>
+        <v>34.60470894775843</v>
       </c>
       <c r="O6" t="n">
-        <v>5.902760363881171</v>
+        <v>5.882576726890898</v>
       </c>
       <c r="P6" t="n">
-        <v>361.7459838198998</v>
+        <v>361.7657699111678</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34743,28 +34987,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1960995492185474</v>
+        <v>0.1918979058984491</v>
       </c>
       <c r="J7" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K7" t="n">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08134591166975447</v>
+        <v>0.07908463858569559</v>
       </c>
       <c r="M7" t="n">
-        <v>3.794705715885602</v>
+        <v>3.784350129565109</v>
       </c>
       <c r="N7" t="n">
-        <v>24.70013075166904</v>
+        <v>24.5870567649224</v>
       </c>
       <c r="O7" t="n">
-        <v>4.969922610229363</v>
+        <v>4.958533731348654</v>
       </c>
       <c r="P7" t="n">
-        <v>369.0042212021721</v>
+        <v>369.0471822597323</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34821,28 +35065,28 @@
         <v>0.0704</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2265557081574527</v>
+        <v>0.2246782881328015</v>
       </c>
       <c r="J8" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K8" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09702026407407383</v>
+        <v>0.09686509823721412</v>
       </c>
       <c r="M8" t="n">
-        <v>3.758971748803317</v>
+        <v>3.739438266648836</v>
       </c>
       <c r="N8" t="n">
-        <v>27.12482988271015</v>
+        <v>26.9418369777417</v>
       </c>
       <c r="O8" t="n">
-        <v>5.208150332191856</v>
+        <v>5.190552665925056</v>
       </c>
       <c r="P8" t="n">
-        <v>365.4092441673124</v>
+        <v>365.4284567863074</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34899,28 +35143,28 @@
         <v>0.0829</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2281551782750698</v>
+        <v>0.2253240083426608</v>
       </c>
       <c r="J9" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K9" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1325144139994237</v>
+        <v>0.1312324435954901</v>
       </c>
       <c r="M9" t="n">
-        <v>3.307247664168117</v>
+        <v>3.297678288138594</v>
       </c>
       <c r="N9" t="n">
-        <v>19.34912189786915</v>
+        <v>19.23964276702552</v>
       </c>
       <c r="O9" t="n">
-        <v>4.398763678338397</v>
+        <v>4.386301718649268</v>
       </c>
       <c r="P9" t="n">
-        <v>366.9304001659849</v>
+        <v>366.9593740179402</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34977,28 +35221,28 @@
         <v>0.0769</v>
       </c>
       <c r="I10" t="n">
-        <v>0.199424008175466</v>
+        <v>0.1971921520307091</v>
       </c>
       <c r="J10" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K10" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1077051097533667</v>
+        <v>0.1069186279132928</v>
       </c>
       <c r="M10" t="n">
-        <v>3.368924393795306</v>
+        <v>3.357470974574757</v>
       </c>
       <c r="N10" t="n">
-        <v>18.70804618721909</v>
+        <v>18.59244888278192</v>
       </c>
       <c r="O10" t="n">
-        <v>4.325279896979973</v>
+        <v>4.311896205010264</v>
       </c>
       <c r="P10" t="n">
-        <v>375.7745306269188</v>
+        <v>375.7973708275706</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35055,28 +35299,28 @@
         <v>0.0823</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1489646289970357</v>
+        <v>0.1489746677074753</v>
       </c>
       <c r="J11" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K11" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07552880314216559</v>
+        <v>0.07661750509784337</v>
       </c>
       <c r="M11" t="n">
-        <v>2.921366240921261</v>
+        <v>2.900879966864051</v>
       </c>
       <c r="N11" t="n">
-        <v>15.42227894634303</v>
+        <v>15.31081012658147</v>
       </c>
       <c r="O11" t="n">
-        <v>3.927120948779529</v>
+        <v>3.912903030562024</v>
       </c>
       <c r="P11" t="n">
-        <v>383.0671808753935</v>
+        <v>383.0670768290457</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35133,28 +35377,28 @@
         <v>0.0887</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1559406660816259</v>
+        <v>0.1589943753533845</v>
       </c>
       <c r="J12" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K12" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07013020763924782</v>
+        <v>0.07361173548346411</v>
       </c>
       <c r="M12" t="n">
-        <v>3.243594054458201</v>
+        <v>3.235778977245172</v>
       </c>
       <c r="N12" t="n">
-        <v>18.30784547205912</v>
+        <v>18.21080727673903</v>
       </c>
       <c r="O12" t="n">
-        <v>4.278766816742777</v>
+        <v>4.267412245933011</v>
       </c>
       <c r="P12" t="n">
-        <v>381.8619074847882</v>
+        <v>381.8306556799826</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35211,28 +35455,28 @@
         <v>0.075</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1746929575085385</v>
+        <v>0.1751189785490887</v>
       </c>
       <c r="J13" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K13" t="n">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07283570679535079</v>
+        <v>0.07420931204036429</v>
       </c>
       <c r="M13" t="n">
-        <v>3.516237704408835</v>
+        <v>3.493327701492954</v>
       </c>
       <c r="N13" t="n">
-        <v>22.09282100267242</v>
+        <v>21.9339503262637</v>
       </c>
       <c r="O13" t="n">
-        <v>4.700300097086613</v>
+        <v>4.683369548334158</v>
       </c>
       <c r="P13" t="n">
-        <v>383.9648368406802</v>
+        <v>383.9604767893073</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35289,28 +35533,28 @@
         <v>0.0617</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2883572370828205</v>
+        <v>0.286204484679942</v>
       </c>
       <c r="J14" t="n">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="K14" t="n">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1743891924862702</v>
+        <v>0.1743188044114492</v>
       </c>
       <c r="M14" t="n">
-        <v>3.494364035675271</v>
+        <v>3.480944748980569</v>
       </c>
       <c r="N14" t="n">
-        <v>22.35902247903995</v>
+        <v>22.2158901013024</v>
       </c>
       <c r="O14" t="n">
-        <v>4.728532804056662</v>
+        <v>4.713373537213277</v>
       </c>
       <c r="P14" t="n">
-        <v>383.527753987569</v>
+        <v>383.5497998444415</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35348,7 +35592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O550"/>
+  <dimension ref="A1:O554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77689,6 +77933,314 @@
         </is>
       </c>
     </row>
+    <row r="551">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>-35.02878548516091,173.91642208297714</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>-35.02931402003588,173.91578356116355</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>-35.029925380972756,173.91527962628626</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-35.030571588073535,173.9148431270444</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-35.03123528580678,173.91445670793686</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>-35.031913797953905,173.9141499127278</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>-35.03262785184519,173.91397111775913</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>-35.033351786357535,173.91380165328152</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>-35.034084742027304,173.91367290221328</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>-35.03480371133679,173.9135374867768</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>-35.0355204590862,173.91342357316532</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>-35.03623630571505,173.91331773270952</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>-35.03695830122412,173.9133218902875</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:11:42+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-35.02878644423654,173.9164236747116</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-35.029314872552746,173.9157849760433</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-35.029925899854724,173.9152805227617</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>-35.03057195434695,173.91484388252547</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>-35.031235935527505,173.91445839577656</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>-35.03191455990894,173.9141529537521</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>-35.03262786896007,173.91397122538737</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>-35.03335221186849,173.91380400883025</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>-35.03408510442276,173.91367471297426</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>-35.034803778398015,173.9135379176265</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>-35.035520470664565,173.9134236818828</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>-35.03623649644785,173.91332134292836</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>-35.03695831158811,173.91332397316225</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-16 22:11:33+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-35.028785112187045,173.91642146396927</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-35.02931513896427,173.91578541819325</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-35.02992813104706,173.91528437760627</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>-35.030573465224734,173.91484699888503</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>-35.03123608840296,173.9144587929153</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>-35.03191500657219,173.9141547364216</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>-35.03262730416906,173.91396767365438</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>-35.03335172833331,173.91380133207034</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>-35.034085829213595,173.9136783344962</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>-35.03480371133679,173.9135374867768</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>-35.03552071381057,173.91342596494988</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>-35.036236328834185,173.91331817031178</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>-35.03695826740454,173.9133150935383</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-24 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-35.02879177243412,173.91643251768156</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-35.02932014750044,173.91579373061256</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-35.02993446140603,173.9152953146082</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>-35.03057644119588,173.9148531371693</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>-35.03123750250088,173.9144624664488</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>-35.03191563715557,173.91415725313144</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>-35.03262738974347,173.91396821179575</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>-35.033350471141546,173.91379437249466</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>-35.03408335639735,173.9136659787156</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>-35.03480416399999,173.91354039501246</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>-35.03552147798338,173.91343314030368</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>-35.03623670451987,173.9133252813489</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>-35.036958245585275,173.9133107085388</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0053/nzd0053.xlsx
+++ b/data/nzd0053/nzd0053.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O554"/>
+  <dimension ref="A1:O556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28700,6 +28700,108 @@
         <v>388.93</v>
       </c>
       <c r="O554" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>363.72</v>
+      </c>
+      <c r="C555" t="n">
+        <v>353.28</v>
+      </c>
+      <c r="D555" t="n">
+        <v>356.97</v>
+      </c>
+      <c r="E555" t="n">
+        <v>361.76</v>
+      </c>
+      <c r="F555" t="n">
+        <v>367.99</v>
+      </c>
+      <c r="G555" t="n">
+        <v>373.21</v>
+      </c>
+      <c r="H555" t="n">
+        <v>369.54</v>
+      </c>
+      <c r="I555" t="n">
+        <v>370.93</v>
+      </c>
+      <c r="J555" t="n">
+        <v>379.9</v>
+      </c>
+      <c r="K555" t="n">
+        <v>387.04</v>
+      </c>
+      <c r="L555" t="n">
+        <v>390.04</v>
+      </c>
+      <c r="M555" t="n">
+        <v>390.43</v>
+      </c>
+      <c r="N555" t="n">
+        <v>389.01</v>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>363.13</v>
+      </c>
+      <c r="C556" t="n">
+        <v>351.95</v>
+      </c>
+      <c r="D556" t="n">
+        <v>355.76</v>
+      </c>
+      <c r="E556" t="n">
+        <v>360.81</v>
+      </c>
+      <c r="F556" t="n">
+        <v>367.54</v>
+      </c>
+      <c r="G556" t="n">
+        <v>372.69</v>
+      </c>
+      <c r="H556" t="n">
+        <v>369.1</v>
+      </c>
+      <c r="I556" t="n">
+        <v>370.46</v>
+      </c>
+      <c r="J556" t="n">
+        <v>379.54</v>
+      </c>
+      <c r="K556" t="n">
+        <v>386.35</v>
+      </c>
+      <c r="L556" t="n">
+        <v>389.26</v>
+      </c>
+      <c r="M556" t="n">
+        <v>389.96</v>
+      </c>
+      <c r="N556" t="n">
+        <v>388.45</v>
+      </c>
+      <c r="O556" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28716,7 +28818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B571"/>
+  <dimension ref="A1:B573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34429,6 +34531,26 @@
       </c>
       <c r="B571" t="n">
         <v>0.58</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -34597,28 +34719,28 @@
         <v>0.0515</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2331223708475704</v>
+        <v>-0.2339043231682218</v>
       </c>
       <c r="J2" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K2" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05439702984685468</v>
+        <v>0.05513865538118212</v>
       </c>
       <c r="M2" t="n">
-        <v>5.413709105222781</v>
+        <v>5.396722844030738</v>
       </c>
       <c r="N2" t="n">
-        <v>54.07807596943245</v>
+        <v>53.88802363738438</v>
       </c>
       <c r="O2" t="n">
-        <v>7.353779706343701</v>
+        <v>7.34084624804146</v>
       </c>
       <c r="P2" t="n">
-        <v>370.741402457949</v>
+        <v>370.7494622588501</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34675,28 +34797,28 @@
         <v>0.0703</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06601859430426414</v>
+        <v>0.06434415841698786</v>
       </c>
       <c r="J3" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K3" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00756578479173875</v>
+        <v>0.007239963545554673</v>
       </c>
       <c r="M3" t="n">
-        <v>4.709181000262263</v>
+        <v>4.698649097558689</v>
       </c>
       <c r="N3" t="n">
-        <v>32.72653151397753</v>
+        <v>32.63097153654146</v>
       </c>
       <c r="O3" t="n">
-        <v>5.720710752518215</v>
+        <v>5.712352539588349</v>
       </c>
       <c r="P3" t="n">
-        <v>353.2741566431814</v>
+        <v>353.2914161207206</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34753,28 +34875,28 @@
         <v>0.0779</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2280395929485828</v>
+        <v>0.2272899159476261</v>
       </c>
       <c r="J4" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K4" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09905730088198783</v>
+        <v>0.09914018815299952</v>
       </c>
       <c r="M4" t="n">
-        <v>4.097533319781316</v>
+        <v>4.084995428448964</v>
       </c>
       <c r="N4" t="n">
-        <v>27.0739039050782</v>
+        <v>26.9818459280894</v>
       </c>
       <c r="O4" t="n">
-        <v>5.203258969634146</v>
+        <v>5.194405252585651</v>
       </c>
       <c r="P4" t="n">
-        <v>351.3898557347065</v>
+        <v>351.397586486013</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34831,28 +34953,28 @@
         <v>0.1156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2744379203732699</v>
+        <v>0.2725569630406703</v>
       </c>
       <c r="J5" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K5" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1490586392179661</v>
+        <v>0.1481553604681215</v>
       </c>
       <c r="M5" t="n">
-        <v>3.635627282499834</v>
+        <v>3.629851731680312</v>
       </c>
       <c r="N5" t="n">
-        <v>24.61219851846509</v>
+        <v>24.55056187160425</v>
       </c>
       <c r="O5" t="n">
-        <v>4.961068283995402</v>
+        <v>4.954852356186231</v>
       </c>
       <c r="P5" t="n">
-        <v>356.7106019366969</v>
+        <v>356.7299872873284</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34909,28 +35031,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2261454645624478</v>
+        <v>0.2261397667498993</v>
       </c>
       <c r="J6" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K6" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0779994321338312</v>
+        <v>0.07855224545056383</v>
       </c>
       <c r="M6" t="n">
-        <v>4.236432507267147</v>
+        <v>4.222005433231193</v>
       </c>
       <c r="N6" t="n">
-        <v>34.60470894775843</v>
+        <v>34.48020501725319</v>
       </c>
       <c r="O6" t="n">
-        <v>5.882576726890898</v>
+        <v>5.871984759623716</v>
       </c>
       <c r="P6" t="n">
-        <v>361.7657699111678</v>
+        <v>361.7658311253329</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34987,28 +35109,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1918979058984491</v>
+        <v>0.1910712190526535</v>
       </c>
       <c r="J7" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K7" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07908463858569559</v>
+        <v>0.07900176560741945</v>
       </c>
       <c r="M7" t="n">
-        <v>3.784350129565109</v>
+        <v>3.774017802391333</v>
       </c>
       <c r="N7" t="n">
-        <v>24.5870567649224</v>
+        <v>24.50363112190346</v>
       </c>
       <c r="O7" t="n">
-        <v>4.958533731348654</v>
+        <v>4.950114253419152</v>
       </c>
       <c r="P7" t="n">
-        <v>369.0471822597323</v>
+        <v>369.0556975100118</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35065,28 +35187,28 @@
         <v>0.0704</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2246782881328015</v>
+        <v>0.2232405749222816</v>
       </c>
       <c r="J8" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K8" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09686509823721412</v>
+        <v>0.09636772486231115</v>
       </c>
       <c r="M8" t="n">
-        <v>3.739438266648836</v>
+        <v>3.731826851185431</v>
       </c>
       <c r="N8" t="n">
-        <v>26.9418369777417</v>
+        <v>26.86026176102026</v>
       </c>
       <c r="O8" t="n">
-        <v>5.190552665925056</v>
+        <v>5.182688661401557</v>
       </c>
       <c r="P8" t="n">
-        <v>365.4284567863074</v>
+        <v>365.4432725186152</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35143,28 +35265,28 @@
         <v>0.0829</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2253240083426608</v>
+        <v>0.2237669888946173</v>
       </c>
       <c r="J9" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K9" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1312324435954901</v>
+        <v>0.1304253132753097</v>
       </c>
       <c r="M9" t="n">
-        <v>3.297678288138594</v>
+        <v>3.293546787110504</v>
       </c>
       <c r="N9" t="n">
-        <v>19.23964276702552</v>
+        <v>19.18849369689682</v>
       </c>
       <c r="O9" t="n">
-        <v>4.386301718649268</v>
+        <v>4.380467292070199</v>
       </c>
       <c r="P9" t="n">
-        <v>366.9593740179402</v>
+        <v>366.9754191411498</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35221,28 +35343,28 @@
         <v>0.0769</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1971921520307091</v>
+        <v>0.1962835703171714</v>
       </c>
       <c r="J10" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K10" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1069186279132928</v>
+        <v>0.1067416159244536</v>
       </c>
       <c r="M10" t="n">
-        <v>3.357470974574757</v>
+        <v>3.350599635165988</v>
       </c>
       <c r="N10" t="n">
-        <v>18.59244888278192</v>
+        <v>18.53169200775076</v>
       </c>
       <c r="O10" t="n">
-        <v>4.311896205010264</v>
+        <v>4.304845178139483</v>
       </c>
       <c r="P10" t="n">
-        <v>375.7973708275706</v>
+        <v>375.8067342627067</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35299,28 +35421,28 @@
         <v>0.0823</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1489746677074753</v>
+        <v>0.1487464975747519</v>
       </c>
       <c r="J11" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K11" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07661750509784337</v>
+        <v>0.07694352603477395</v>
       </c>
       <c r="M11" t="n">
-        <v>2.900879966864051</v>
+        <v>2.891688886220702</v>
       </c>
       <c r="N11" t="n">
-        <v>15.31081012658147</v>
+        <v>15.25645150109613</v>
       </c>
       <c r="O11" t="n">
-        <v>3.912903030562024</v>
+        <v>3.905950780680183</v>
       </c>
       <c r="P11" t="n">
-        <v>383.0670768290457</v>
+        <v>383.0694314558138</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35377,28 +35499,28 @@
         <v>0.0887</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1589943753533845</v>
+        <v>0.1614864110198154</v>
       </c>
       <c r="J12" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K12" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07361173548346411</v>
+        <v>0.07612252405843123</v>
       </c>
       <c r="M12" t="n">
-        <v>3.235778977245172</v>
+        <v>3.236911632559121</v>
       </c>
       <c r="N12" t="n">
-        <v>18.21080727673903</v>
+        <v>18.19185609557773</v>
       </c>
       <c r="O12" t="n">
-        <v>4.267412245933011</v>
+        <v>4.265191214421427</v>
       </c>
       <c r="P12" t="n">
-        <v>381.8306556799826</v>
+        <v>381.8049836009424</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35455,28 +35577,28 @@
         <v>0.075</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1751189785490887</v>
+        <v>0.1762161970083932</v>
       </c>
       <c r="J13" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K13" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07420931204036429</v>
+        <v>0.07558012875112829</v>
       </c>
       <c r="M13" t="n">
-        <v>3.493327701492954</v>
+        <v>3.487245920338661</v>
       </c>
       <c r="N13" t="n">
-        <v>21.9339503262637</v>
+        <v>21.86393766879776</v>
       </c>
       <c r="O13" t="n">
-        <v>4.683369548334158</v>
+        <v>4.675888970965603</v>
       </c>
       <c r="P13" t="n">
-        <v>383.9604767893073</v>
+        <v>383.9491801767668</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35533,28 +35655,28 @@
         <v>0.0617</v>
       </c>
       <c r="I14" t="n">
-        <v>0.286204484679942</v>
+        <v>0.2845274303552377</v>
       </c>
       <c r="J14" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="K14" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1743188044114492</v>
+        <v>0.1736007433835848</v>
       </c>
       <c r="M14" t="n">
-        <v>3.480944748980569</v>
+        <v>3.477644479636343</v>
       </c>
       <c r="N14" t="n">
-        <v>22.2158901013024</v>
+        <v>22.15685621970037</v>
       </c>
       <c r="O14" t="n">
-        <v>4.713373537213277</v>
+        <v>4.70710699046669</v>
       </c>
       <c r="P14" t="n">
-        <v>383.5497998444415</v>
+        <v>383.5670910444545</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35592,7 +35714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O554"/>
+  <dimension ref="A1:O556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78241,6 +78363,160 @@
         </is>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-35.02878745659414,173.9164253548758</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-35.02932233207455,173.9157973562426</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-35.02993331986597,173.91529334236185</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>-35.03056430838843,173.9148281118592</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>-35.03124239451439,173.91447517489001</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>-35.03192018260919,173.91417539441616</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>-35.03262675649283,173.9139642295497</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>-35.033351592943454,173.91380058257755</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>-35.03408576526146,173.91367801495016</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>-35.03480389575514,173.91353867161354</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>-35.035522925279224,173.9134467299892</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>-35.03623735185424,173.91333753421296</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>-35.03695824994914,173.91331158553874</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-35.02878431295732,173.91642013752391</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-35.02931524552886,173.91578559505322</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-35.029927041395005,173.91528249500774</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>-35.03055995889011,173.91481914052343</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>-35.031240674666044,173.9144707070785</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>-35.031918816345964,173.91416994154426</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>-35.032626003437855,173.91395949390582</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>-35.03335068389709,173.91379555026901</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>-35.03408499783586,173.9136741803975</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>-35.03480273894897,173.91353123945584</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>-35.0355220221668,173.9134382500254</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>-35.03623708020514,173.91333239238605</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>-35.03695821940193,173.91330544653945</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0053/nzd0053.xlsx
+++ b/data/nzd0053/nzd0053.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O556"/>
+  <dimension ref="A1:O558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28802,6 +28802,108 @@
         <v>388.45</v>
       </c>
       <c r="O556" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>361.97</v>
+      </c>
+      <c r="C557" t="n">
+        <v>350.51</v>
+      </c>
+      <c r="D557" t="n">
+        <v>355.09</v>
+      </c>
+      <c r="E557" t="n">
+        <v>360.36</v>
+      </c>
+      <c r="F557" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="G557" t="n">
+        <v>372.1</v>
+      </c>
+      <c r="H557" t="n">
+        <v>369.29</v>
+      </c>
+      <c r="I557" t="n">
+        <v>371.62</v>
+      </c>
+      <c r="J557" t="n">
+        <v>380.37</v>
+      </c>
+      <c r="K557" t="n">
+        <v>386.66</v>
+      </c>
+      <c r="L557" t="n">
+        <v>389.23</v>
+      </c>
+      <c r="M557" t="n">
+        <v>389.42</v>
+      </c>
+      <c r="N557" t="n">
+        <v>388.41</v>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>361.42</v>
+      </c>
+      <c r="C558" t="n">
+        <v>349.14</v>
+      </c>
+      <c r="D558" t="n">
+        <v>353.56</v>
+      </c>
+      <c r="E558" t="n">
+        <v>359.79</v>
+      </c>
+      <c r="F558" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="G558" t="n">
+        <v>371.63</v>
+      </c>
+      <c r="H558" t="n">
+        <v>368.21</v>
+      </c>
+      <c r="I558" t="n">
+        <v>370.86</v>
+      </c>
+      <c r="J558" t="n">
+        <v>379.28</v>
+      </c>
+      <c r="K558" t="n">
+        <v>385.34</v>
+      </c>
+      <c r="L558" t="n">
+        <v>387.9</v>
+      </c>
+      <c r="M558" t="n">
+        <v>388.59</v>
+      </c>
+      <c r="N558" t="n">
+        <v>388.48</v>
+      </c>
+      <c r="O558" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28818,7 +28920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B573"/>
+  <dimension ref="A1:B575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34550,6 +34652,26 @@
         </is>
       </c>
       <c r="B573" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
         <v>0.8100000000000001</v>
       </c>
     </row>
@@ -34719,28 +34841,28 @@
         <v>0.0515</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2339043231682218</v>
+        <v>-0.235854365330335</v>
       </c>
       <c r="J2" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K2" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05513865538118212</v>
+        <v>0.05639170293326878</v>
       </c>
       <c r="M2" t="n">
-        <v>5.396722844030738</v>
+        <v>5.383544400589869</v>
       </c>
       <c r="N2" t="n">
-        <v>53.88802363738438</v>
+        <v>53.72308075364266</v>
       </c>
       <c r="O2" t="n">
-        <v>7.34084624804146</v>
+        <v>7.329603042023671</v>
       </c>
       <c r="P2" t="n">
-        <v>370.7494622588501</v>
+        <v>370.7696368724822</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34797,28 +34919,28 @@
         <v>0.0703</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06434415841698786</v>
+        <v>0.06076476915614525</v>
       </c>
       <c r="J3" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K3" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007239963545554673</v>
+        <v>0.006492473569969404</v>
       </c>
       <c r="M3" t="n">
-        <v>4.698649097558689</v>
+        <v>4.695401129071035</v>
       </c>
       <c r="N3" t="n">
-        <v>32.63097153654146</v>
+        <v>32.61078148619284</v>
       </c>
       <c r="O3" t="n">
-        <v>5.712352539588349</v>
+        <v>5.71058503887236</v>
       </c>
       <c r="P3" t="n">
-        <v>353.2914161207206</v>
+        <v>353.3284495260365</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34875,28 +34997,28 @@
         <v>0.0779</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2272899159476261</v>
+        <v>0.2251253460426162</v>
       </c>
       <c r="J4" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K4" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09914018815299952</v>
+        <v>0.09800400454564562</v>
       </c>
       <c r="M4" t="n">
-        <v>4.084995428448964</v>
+        <v>4.07667154402897</v>
       </c>
       <c r="N4" t="n">
-        <v>26.9818459280894</v>
+        <v>26.92192468176722</v>
       </c>
       <c r="O4" t="n">
-        <v>5.194405252585651</v>
+        <v>5.188634182688852</v>
       </c>
       <c r="P4" t="n">
-        <v>351.397586486013</v>
+        <v>351.419985545939</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34953,28 +35075,28 @@
         <v>0.1156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2725569630406703</v>
+        <v>0.2698515620329512</v>
       </c>
       <c r="J5" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K5" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1481553604681215</v>
+        <v>0.1463394108333098</v>
       </c>
       <c r="M5" t="n">
-        <v>3.629851731680312</v>
+        <v>3.627276614549594</v>
       </c>
       <c r="N5" t="n">
-        <v>24.55056187160425</v>
+        <v>24.51716968082957</v>
       </c>
       <c r="O5" t="n">
-        <v>4.954852356186231</v>
+        <v>4.951481564221922</v>
       </c>
       <c r="P5" t="n">
-        <v>356.7299872873284</v>
+        <v>356.7579757606869</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35031,28 +35153,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2261397667498993</v>
+        <v>0.2253137005997299</v>
       </c>
       <c r="J6" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K6" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07855224545056383</v>
+        <v>0.07856918993835516</v>
       </c>
       <c r="M6" t="n">
-        <v>4.222005433231193</v>
+        <v>4.21047158057099</v>
       </c>
       <c r="N6" t="n">
-        <v>34.48020501725319</v>
+        <v>34.36229689407542</v>
       </c>
       <c r="O6" t="n">
-        <v>5.871984759623716</v>
+        <v>5.861936275163303</v>
       </c>
       <c r="P6" t="n">
-        <v>361.7658311253329</v>
+        <v>361.7743812763525</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35109,28 +35231,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1910712190526535</v>
+        <v>0.1894924635890631</v>
       </c>
       <c r="J7" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K7" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07900176560741945</v>
+        <v>0.07830299694834242</v>
       </c>
       <c r="M7" t="n">
-        <v>3.774017802391333</v>
+        <v>3.766743310173857</v>
       </c>
       <c r="N7" t="n">
-        <v>24.50363112190346</v>
+        <v>24.43427807934863</v>
       </c>
       <c r="O7" t="n">
-        <v>4.950114253419152</v>
+        <v>4.943104093517415</v>
       </c>
       <c r="P7" t="n">
-        <v>369.0556975100118</v>
+        <v>369.0720211612712</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35187,28 +35309,28 @@
         <v>0.0704</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2232405749222816</v>
+        <v>0.2214129607829989</v>
       </c>
       <c r="J8" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K8" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09636772486231115</v>
+        <v>0.09552777843108029</v>
       </c>
       <c r="M8" t="n">
-        <v>3.731826851185431</v>
+        <v>3.725792380517137</v>
       </c>
       <c r="N8" t="n">
-        <v>26.86026176102026</v>
+        <v>26.78971938881308</v>
       </c>
       <c r="O8" t="n">
-        <v>5.182688661401557</v>
+        <v>5.175878610324346</v>
       </c>
       <c r="P8" t="n">
-        <v>365.4432725186152</v>
+        <v>365.462183631267</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35265,28 +35387,28 @@
         <v>0.0829</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2237669888946173</v>
+        <v>0.2225934210373854</v>
       </c>
       <c r="J9" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K9" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1304253132753097</v>
+        <v>0.1300452189472479</v>
       </c>
       <c r="M9" t="n">
-        <v>3.293546787110504</v>
+        <v>3.287498278888772</v>
       </c>
       <c r="N9" t="n">
-        <v>19.18849369689682</v>
+        <v>19.13037432278242</v>
       </c>
       <c r="O9" t="n">
-        <v>4.380467292070199</v>
+        <v>4.37382833714155</v>
       </c>
       <c r="P9" t="n">
-        <v>366.9754191411498</v>
+        <v>366.9875629559905</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35343,28 +35465,28 @@
         <v>0.0769</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1962835703171714</v>
+        <v>0.1954474479175669</v>
       </c>
       <c r="J10" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K10" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1067416159244536</v>
+        <v>0.1066316995659193</v>
       </c>
       <c r="M10" t="n">
-        <v>3.350599635165988</v>
+        <v>3.343322610590604</v>
       </c>
       <c r="N10" t="n">
-        <v>18.53169200775076</v>
+        <v>18.47143964799398</v>
       </c>
       <c r="O10" t="n">
-        <v>4.304845178139483</v>
+        <v>4.297841277664169</v>
       </c>
       <c r="P10" t="n">
-        <v>375.8067342627067</v>
+        <v>375.8153892033522</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35421,28 +35543,28 @@
         <v>0.0823</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1487464975747519</v>
+        <v>0.1480340331360957</v>
       </c>
       <c r="J11" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K11" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07694352603477395</v>
+        <v>0.07678534817303384</v>
       </c>
       <c r="M11" t="n">
-        <v>2.891688886220702</v>
+        <v>2.885007947867877</v>
       </c>
       <c r="N11" t="n">
-        <v>15.25645150109613</v>
+        <v>15.20701603716625</v>
       </c>
       <c r="O11" t="n">
-        <v>3.905950780680183</v>
+        <v>3.899617421897468</v>
       </c>
       <c r="P11" t="n">
-        <v>383.0694314558138</v>
+        <v>383.0768084197694</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35499,28 +35621,28 @@
         <v>0.0887</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1614864110198154</v>
+        <v>0.163182928365124</v>
       </c>
       <c r="J12" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K12" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07612252405843123</v>
+        <v>0.07806880325432275</v>
       </c>
       <c r="M12" t="n">
-        <v>3.236911632559121</v>
+        <v>3.233955002949783</v>
       </c>
       <c r="N12" t="n">
-        <v>18.19185609557773</v>
+        <v>18.14959608797533</v>
       </c>
       <c r="O12" t="n">
-        <v>4.265191214421427</v>
+        <v>4.260234276184272</v>
       </c>
       <c r="P12" t="n">
-        <v>381.8049836009424</v>
+        <v>381.7874415040691</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35577,28 +35699,28 @@
         <v>0.075</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1762161970083932</v>
+        <v>0.1764645716519486</v>
       </c>
       <c r="J13" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K13" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07558012875112829</v>
+        <v>0.076316048744557</v>
       </c>
       <c r="M13" t="n">
-        <v>3.487245920338661</v>
+        <v>3.476397133379534</v>
       </c>
       <c r="N13" t="n">
-        <v>21.86393766879776</v>
+        <v>21.7863896182175</v>
       </c>
       <c r="O13" t="n">
-        <v>4.675888970965603</v>
+        <v>4.667589272656443</v>
       </c>
       <c r="P13" t="n">
-        <v>383.9491801767668</v>
+        <v>383.9466166982666</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35655,28 +35777,28 @@
         <v>0.0617</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2845274303552377</v>
+        <v>0.2826600082227511</v>
       </c>
       <c r="J14" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K14" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1736007433835848</v>
+        <v>0.1726520955619759</v>
       </c>
       <c r="M14" t="n">
-        <v>3.477644479636343</v>
+        <v>3.47546726513974</v>
       </c>
       <c r="N14" t="n">
-        <v>22.15685621970037</v>
+        <v>22.10313995673668</v>
       </c>
       <c r="O14" t="n">
-        <v>4.70710699046669</v>
+        <v>4.701397659923768</v>
       </c>
       <c r="P14" t="n">
-        <v>383.5670910444545</v>
+        <v>383.5864178475177</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35714,7 +35836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O556"/>
+  <dimension ref="A1:O558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78517,6 +78639,160 @@
         </is>
       </c>
     </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-35.02877813224699,173.91640987968074</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-35.02930757287658,173.9157728611362</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-35.02992356488585,173.9152764886223</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>-35.03055789860119,173.91481489094363</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>-35.0312388783798,173.91446604069773</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-35.03191726616238,173.9141637546321</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-35.03262632862071,173.91396153884295</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>-35.03335292750046,173.91380797043502</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>-35.034086767178046,173.9136830211718</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>-35.03480325867353,173.91353457854115</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>-35.03552198743169,173.91343792387295</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>-35.03623676809741,173.91332648475517</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>-35.03695821721998,173.9133050080395</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-35.02877520173746,173.9164050160487</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-35.02930027319916,173.91576074623123</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-35.02991562599068,173.91526277254997</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>-35.03055528890169,173.91480950814287</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>-35.03123524758793,173.9144566086522</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>-35.03191603127016,173.91415882607512</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>-35.03262448021246,173.91394991499004</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>-35.03335145755358,173.91379983308477</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>-35.034084443583964,173.91367141099838</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>-35.03480104565213,173.91352036050068</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>-35.035520447507814,173.91342346444785</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>-35.036236288375704,173.91331740450778</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>-35.0369582210384,173.91330577541441</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0053/nzd0053.xlsx
+++ b/data/nzd0053/nzd0053.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O558"/>
+  <dimension ref="A1:O561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28904,6 +28904,159 @@
         <v>388.48</v>
       </c>
       <c r="O558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>360.75</v>
+      </c>
+      <c r="C559" t="n">
+        <v>349.29</v>
+      </c>
+      <c r="D559" t="n">
+        <v>353.36</v>
+      </c>
+      <c r="E559" t="n">
+        <v>359.94</v>
+      </c>
+      <c r="F559" t="n">
+        <v>365.51</v>
+      </c>
+      <c r="G559" t="n">
+        <v>371.46</v>
+      </c>
+      <c r="H559" t="n">
+        <v>368.33</v>
+      </c>
+      <c r="I559" t="n">
+        <v>370.68</v>
+      </c>
+      <c r="J559" t="n">
+        <v>379.15</v>
+      </c>
+      <c r="K559" t="n">
+        <v>385.22</v>
+      </c>
+      <c r="L559" t="n">
+        <v>387.76</v>
+      </c>
+      <c r="M559" t="n">
+        <v>388.19</v>
+      </c>
+      <c r="N559" t="n">
+        <v>388.48</v>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>360.4</v>
+      </c>
+      <c r="C560" t="n">
+        <v>348.41</v>
+      </c>
+      <c r="D560" t="n">
+        <v>352.82</v>
+      </c>
+      <c r="E560" t="n">
+        <v>359.93</v>
+      </c>
+      <c r="F560" t="n">
+        <v>365.49</v>
+      </c>
+      <c r="G560" t="n">
+        <v>371.58</v>
+      </c>
+      <c r="H560" t="n">
+        <v>368.49</v>
+      </c>
+      <c r="I560" t="n">
+        <v>370.57</v>
+      </c>
+      <c r="J560" t="n">
+        <v>378.76</v>
+      </c>
+      <c r="K560" t="n">
+        <v>384.44</v>
+      </c>
+      <c r="L560" t="n">
+        <v>387.04</v>
+      </c>
+      <c r="M560" t="n">
+        <v>387.75</v>
+      </c>
+      <c r="N560" t="n">
+        <v>388.47</v>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>360.48</v>
+      </c>
+      <c r="C561" t="n">
+        <v>347.6</v>
+      </c>
+      <c r="D561" t="n">
+        <v>351.12</v>
+      </c>
+      <c r="E561" t="n">
+        <v>359.57</v>
+      </c>
+      <c r="F561" t="n">
+        <v>364.6</v>
+      </c>
+      <c r="G561" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="H561" t="n">
+        <v>367.27</v>
+      </c>
+      <c r="I561" t="n">
+        <v>369.49</v>
+      </c>
+      <c r="J561" t="n">
+        <v>378.48</v>
+      </c>
+      <c r="K561" t="n">
+        <v>383.33</v>
+      </c>
+      <c r="L561" t="n">
+        <v>385.06</v>
+      </c>
+      <c r="M561" t="n">
+        <v>387.03</v>
+      </c>
+      <c r="N561" t="n">
+        <v>388.26</v>
+      </c>
+      <c r="O561" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28920,7 +29073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B575"/>
+  <dimension ref="A1:B578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34673,6 +34826,36 @@
       </c>
       <c r="B575" t="n">
         <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>
@@ -34841,28 +35024,28 @@
         <v>0.0515</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.235854365330335</v>
+        <v>-0.2398794096721037</v>
       </c>
       <c r="J2" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K2" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05639170293326878</v>
+        <v>0.05877150730639524</v>
       </c>
       <c r="M2" t="n">
-        <v>5.383544400589869</v>
+        <v>5.367504297636115</v>
       </c>
       <c r="N2" t="n">
-        <v>53.72308075364266</v>
+        <v>53.51647939686642</v>
       </c>
       <c r="O2" t="n">
-        <v>7.329603042023671</v>
+        <v>7.31549584080713</v>
       </c>
       <c r="P2" t="n">
-        <v>370.7696368724822</v>
+        <v>370.8114208442916</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34919,28 +35102,28 @@
         <v>0.0703</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06076476915614525</v>
+        <v>0.05407233021114818</v>
       </c>
       <c r="J3" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K3" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006492473569969404</v>
+        <v>0.005171530918404943</v>
       </c>
       <c r="M3" t="n">
-        <v>4.695401129071035</v>
+        <v>4.695508339857471</v>
       </c>
       <c r="N3" t="n">
-        <v>32.61078148619284</v>
+        <v>32.66273948288126</v>
       </c>
       <c r="O3" t="n">
-        <v>5.71058503887236</v>
+        <v>5.715132499153564</v>
       </c>
       <c r="P3" t="n">
-        <v>353.3284495260365</v>
+        <v>353.3979283639868</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34997,28 +35180,28 @@
         <v>0.0779</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2251253460426162</v>
+        <v>0.2199919061476457</v>
       </c>
       <c r="J4" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K4" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09800400454564562</v>
+        <v>0.09455092898891704</v>
       </c>
       <c r="M4" t="n">
-        <v>4.07667154402897</v>
+        <v>4.070076143500913</v>
       </c>
       <c r="N4" t="n">
-        <v>26.92192468176722</v>
+        <v>26.91441774574315</v>
       </c>
       <c r="O4" t="n">
-        <v>5.188634182688852</v>
+        <v>5.187910730317471</v>
       </c>
       <c r="P4" t="n">
-        <v>351.419985545939</v>
+        <v>351.4732827890444</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35075,28 +35258,28 @@
         <v>0.1156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2698515620329512</v>
+        <v>0.2655861284997495</v>
       </c>
       <c r="J5" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K5" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1463394108333098</v>
+        <v>0.1433587237996129</v>
       </c>
       <c r="M5" t="n">
-        <v>3.627276614549594</v>
+        <v>3.624556267058225</v>
       </c>
       <c r="N5" t="n">
-        <v>24.51716968082957</v>
+        <v>24.47704593957765</v>
       </c>
       <c r="O5" t="n">
-        <v>4.951481564221922</v>
+        <v>4.947428214696767</v>
       </c>
       <c r="P5" t="n">
-        <v>356.7579757606869</v>
+        <v>356.8022555247894</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35153,28 +35336,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2253137005997299</v>
+        <v>0.2226508087475507</v>
       </c>
       <c r="J6" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K6" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07856918993835516</v>
+        <v>0.07761107967548131</v>
       </c>
       <c r="M6" t="n">
-        <v>4.21047158057099</v>
+        <v>4.199455551807656</v>
       </c>
       <c r="N6" t="n">
-        <v>34.36229689407542</v>
+        <v>34.21466268276373</v>
       </c>
       <c r="O6" t="n">
-        <v>5.861936275163303</v>
+        <v>5.849330105470517</v>
       </c>
       <c r="P6" t="n">
-        <v>361.7743812763525</v>
+        <v>361.8020274516074</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35231,28 +35414,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1894924635890631</v>
+        <v>0.1866666413153683</v>
       </c>
       <c r="J7" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K7" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07830299694834242</v>
+        <v>0.07685908787421492</v>
       </c>
       <c r="M7" t="n">
-        <v>3.766743310173857</v>
+        <v>3.757720609662248</v>
       </c>
       <c r="N7" t="n">
-        <v>24.43427807934863</v>
+        <v>24.34343008841355</v>
       </c>
       <c r="O7" t="n">
-        <v>4.943104093517415</v>
+        <v>4.933906169396977</v>
       </c>
       <c r="P7" t="n">
-        <v>369.0720211612712</v>
+        <v>369.1013390609417</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35309,28 +35492,28 @@
         <v>0.0704</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2214129607829989</v>
+        <v>0.2179760207671295</v>
       </c>
       <c r="J8" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K8" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09552777843108029</v>
+        <v>0.0936413158043895</v>
       </c>
       <c r="M8" t="n">
-        <v>3.725792380517137</v>
+        <v>3.720051579533564</v>
       </c>
       <c r="N8" t="n">
-        <v>26.78971938881308</v>
+        <v>26.70689439698754</v>
       </c>
       <c r="O8" t="n">
-        <v>5.175878610324346</v>
+        <v>5.167871360336627</v>
       </c>
       <c r="P8" t="n">
-        <v>365.462183631267</v>
+        <v>365.497865559073</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35387,28 +35570,28 @@
         <v>0.0829</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2225934210373854</v>
+        <v>0.2198322420783191</v>
       </c>
       <c r="J9" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K9" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1300452189472479</v>
+        <v>0.1283000847830036</v>
       </c>
       <c r="M9" t="n">
-        <v>3.287498278888772</v>
+        <v>3.283462638196945</v>
       </c>
       <c r="N9" t="n">
-        <v>19.13037432278242</v>
+        <v>19.06760713596264</v>
       </c>
       <c r="O9" t="n">
-        <v>4.37382833714155</v>
+        <v>4.366647127483814</v>
       </c>
       <c r="P9" t="n">
-        <v>366.9875629559905</v>
+        <v>367.0162304853699</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35465,28 +35648,28 @@
         <v>0.0769</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1954474479175669</v>
+        <v>0.1931477798285965</v>
       </c>
       <c r="J10" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K10" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1066316995659193</v>
+        <v>0.1053431847338748</v>
       </c>
       <c r="M10" t="n">
-        <v>3.343322610590604</v>
+        <v>3.338343065633705</v>
       </c>
       <c r="N10" t="n">
-        <v>18.47143964799398</v>
+        <v>18.3993647061234</v>
       </c>
       <c r="O10" t="n">
-        <v>4.297841277664169</v>
+        <v>4.289448065441917</v>
       </c>
       <c r="P10" t="n">
-        <v>375.8153892033522</v>
+        <v>375.8392640322446</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35543,28 +35726,28 @@
         <v>0.0823</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1480340331360957</v>
+        <v>0.1452614868942237</v>
       </c>
       <c r="J11" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K11" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07678534817303384</v>
+        <v>0.07475260438954268</v>
       </c>
       <c r="M11" t="n">
-        <v>2.885007947867877</v>
+        <v>2.884021204018507</v>
       </c>
       <c r="N11" t="n">
-        <v>15.20701603716625</v>
+        <v>15.1672159401183</v>
       </c>
       <c r="O11" t="n">
-        <v>3.899617421897468</v>
+        <v>3.894511001411898</v>
       </c>
       <c r="P11" t="n">
-        <v>383.0768084197694</v>
+        <v>383.1055965636505</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35621,28 +35804,28 @@
         <v>0.0887</v>
       </c>
       <c r="I12" t="n">
-        <v>0.163182928365124</v>
+        <v>0.1636617849788841</v>
       </c>
       <c r="J12" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K12" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07806880325432275</v>
+        <v>0.07929697607920561</v>
       </c>
       <c r="M12" t="n">
-        <v>3.233955002949783</v>
+        <v>3.223009176852836</v>
       </c>
       <c r="N12" t="n">
-        <v>18.14959608797533</v>
+        <v>18.06054562487475</v>
       </c>
       <c r="O12" t="n">
-        <v>4.260234276184272</v>
+        <v>4.249770067294787</v>
       </c>
       <c r="P12" t="n">
-        <v>381.7874415040691</v>
+        <v>381.7824806424682</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35699,28 +35882,28 @@
         <v>0.075</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1764645716519486</v>
+        <v>0.1754339828464603</v>
       </c>
       <c r="J13" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K13" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L13" t="n">
-        <v>0.076316048744557</v>
+        <v>0.07628148978966964</v>
       </c>
       <c r="M13" t="n">
-        <v>3.476397133379534</v>
+        <v>3.462281835560373</v>
       </c>
       <c r="N13" t="n">
-        <v>21.7863896182175</v>
+        <v>21.67603615424799</v>
       </c>
       <c r="O13" t="n">
-        <v>4.667589272656443</v>
+        <v>4.655753016886527</v>
       </c>
       <c r="P13" t="n">
-        <v>383.9466166982666</v>
+        <v>383.9573140687193</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35777,28 +35960,28 @@
         <v>0.0617</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2826600082227511</v>
+        <v>0.2798536406069263</v>
       </c>
       <c r="J14" t="n">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="K14" t="n">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1726520955619759</v>
+        <v>0.1711963923231262</v>
       </c>
       <c r="M14" t="n">
-        <v>3.47546726513974</v>
+        <v>3.472300057000643</v>
       </c>
       <c r="N14" t="n">
-        <v>22.10313995673668</v>
+        <v>22.0240337169985</v>
       </c>
       <c r="O14" t="n">
-        <v>4.701397659923768</v>
+        <v>4.692977063336076</v>
       </c>
       <c r="P14" t="n">
-        <v>383.5864178475177</v>
+        <v>383.6155662050612</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35836,7 +36019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O558"/>
+  <dimension ref="A1:O561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78793,6 +78976,237 @@
         </is>
       </c>
     </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-35.028771631843775,173.91639909126107</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-35.02930107243398,173.91576207268056</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-35.02991458822649,173.91526097959954</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-35.03055597566474,173.91481092466935</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>-35.03123291623695,173.91445055228652</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>-35.03191558460695,173.91415704340562</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>-35.032624685591216,173.91395120652925</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>-35.03335110940818,173.91379790581766</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>-35.03408416645798,173.91367002629883</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>-35.03480084446827,173.91351906795157</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>-35.03552028541047,173.91342194240312</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>-35.03623605718427,173.913313028485</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>-35.0369582210384,173.91330577541441</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-35.02876976697382,173.91639599622297</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-35.02929638358952,173.91575429084477</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-35.02991178626303,173.91525613863357</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-35.030555929880535,173.91481083023427</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>-35.031232839799216,173.91445035371717</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>-35.031915899898635,173.91415830176058</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-35.03262495942952,173.9139529285815</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>-35.03335089665264,173.91379672804334</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>-35.03408333507997,173.91366587220026</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>-35.03479953677293,173.9135106663826</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>-35.035519451766646,173.91341411474465</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>-35.036235802873506,173.91330821485994</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>-35.03695822049292,173.9133056657894</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-35.02877019322981,173.91639670366024</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-35.02929206772085,173.91574712801943</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-35.02990296526565,173.91524089855776</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>-35.03055428164918,173.91480743057076</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>-35.03122943831936,173.91444151738102</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>-35.03191463873188,173.91415326834084</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>-35.032622871411775,173.91393979793332</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>-35.033348807779504,173.913785164441</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>-35.03408273819309,173.91366288977056</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>-35.03479767582084,173.9134987103041</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>-35.03551715924352,173.91339258868464</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>-35.03623538672822,173.91330033801898</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>-35.036958209037635,173.91330336366468</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0053/nzd0053.xlsx
+++ b/data/nzd0053/nzd0053.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O561"/>
+  <dimension ref="A1:O564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29057,6 +29057,159 @@
         <v>388.26</v>
       </c>
       <c r="O561" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>359.9</v>
+      </c>
+      <c r="C562" t="n">
+        <v>346.88</v>
+      </c>
+      <c r="D562" t="n">
+        <v>350.78</v>
+      </c>
+      <c r="E562" t="n">
+        <v>359.64</v>
+      </c>
+      <c r="F562" t="n">
+        <v>364.05</v>
+      </c>
+      <c r="G562" t="n">
+        <v>371.28</v>
+      </c>
+      <c r="H562" t="n">
+        <v>366.81</v>
+      </c>
+      <c r="I562" t="n">
+        <v>369.27</v>
+      </c>
+      <c r="J562" t="n">
+        <v>377.39</v>
+      </c>
+      <c r="K562" t="n">
+        <v>382.73</v>
+      </c>
+      <c r="L562" t="n">
+        <v>384.77</v>
+      </c>
+      <c r="M562" t="n">
+        <v>386.1</v>
+      </c>
+      <c r="N562" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>357.47</v>
+      </c>
+      <c r="C563" t="n">
+        <v>346.86</v>
+      </c>
+      <c r="D563" t="n">
+        <v>348.84</v>
+      </c>
+      <c r="E563" t="n">
+        <v>358.96</v>
+      </c>
+      <c r="F563" t="n">
+        <v>362.69</v>
+      </c>
+      <c r="G563" t="n">
+        <v>370.65</v>
+      </c>
+      <c r="H563" t="n">
+        <v>365.39</v>
+      </c>
+      <c r="I563" t="n">
+        <v>368.19</v>
+      </c>
+      <c r="J563" t="n">
+        <v>375.47</v>
+      </c>
+      <c r="K563" t="n">
+        <v>381.99</v>
+      </c>
+      <c r="L563" t="n">
+        <v>383.39</v>
+      </c>
+      <c r="M563" t="n">
+        <v>384.87</v>
+      </c>
+      <c r="N563" t="n">
+        <v>388.75</v>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>358.01</v>
+      </c>
+      <c r="C564" t="n">
+        <v>347.04</v>
+      </c>
+      <c r="D564" t="n">
+        <v>349.43</v>
+      </c>
+      <c r="E564" t="n">
+        <v>359.72</v>
+      </c>
+      <c r="F564" t="n">
+        <v>364.01</v>
+      </c>
+      <c r="G564" t="n">
+        <v>371.92</v>
+      </c>
+      <c r="H564" t="n">
+        <v>367</v>
+      </c>
+      <c r="I564" t="n">
+        <v>369.19</v>
+      </c>
+      <c r="J564" t="n">
+        <v>376.57</v>
+      </c>
+      <c r="K564" t="n">
+        <v>382.95</v>
+      </c>
+      <c r="L564" t="n">
+        <v>384.3</v>
+      </c>
+      <c r="M564" t="n">
+        <v>386.64</v>
+      </c>
+      <c r="N564" t="n">
+        <v>390.24</v>
+      </c>
+      <c r="O564" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29073,7 +29226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B578"/>
+  <dimension ref="A1:B581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34856,6 +35009,36 @@
       </c>
       <c r="B578" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -35024,28 +35207,28 @@
         <v>0.0515</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2398794096721037</v>
+        <v>-0.2458990735483552</v>
       </c>
       <c r="J2" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K2" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05877150730639524</v>
+        <v>0.06203308707736555</v>
       </c>
       <c r="M2" t="n">
-        <v>5.367504297636115</v>
+        <v>5.358047364833475</v>
       </c>
       <c r="N2" t="n">
-        <v>53.51647939686642</v>
+        <v>53.42060712211582</v>
       </c>
       <c r="O2" t="n">
-        <v>7.31549584080713</v>
+        <v>7.308940218808457</v>
       </c>
       <c r="P2" t="n">
-        <v>370.8114208442916</v>
+        <v>370.8741642629208</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35102,28 +35285,28 @@
         <v>0.0703</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05407233021114818</v>
+        <v>0.04602243421231782</v>
       </c>
       <c r="J3" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K3" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005171530918404943</v>
+        <v>0.003756939215153965</v>
       </c>
       <c r="M3" t="n">
-        <v>4.695508339857471</v>
+        <v>4.700514674840425</v>
       </c>
       <c r="N3" t="n">
-        <v>32.66273948288126</v>
+        <v>32.81717720175883</v>
       </c>
       <c r="O3" t="n">
-        <v>5.715132499153564</v>
+        <v>5.728627863787176</v>
       </c>
       <c r="P3" t="n">
-        <v>353.3979283639868</v>
+        <v>353.4818237571648</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35180,28 +35363,28 @@
         <v>0.0779</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2199919061476457</v>
+        <v>0.2121730726676515</v>
       </c>
       <c r="J4" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K4" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09455092898891704</v>
+        <v>0.08851985207573387</v>
       </c>
       <c r="M4" t="n">
-        <v>4.070076143500913</v>
+        <v>4.07232116706148</v>
       </c>
       <c r="N4" t="n">
-        <v>26.91441774574315</v>
+        <v>27.08432249673299</v>
       </c>
       <c r="O4" t="n">
-        <v>5.187910730317471</v>
+        <v>5.204260033543001</v>
       </c>
       <c r="P4" t="n">
-        <v>351.4732827890444</v>
+        <v>351.5547753359085</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35258,28 +35441,28 @@
         <v>0.1156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2655861284997495</v>
+        <v>0.261027926612637</v>
       </c>
       <c r="J5" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K5" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1433587237996129</v>
+        <v>0.1400141290218831</v>
       </c>
       <c r="M5" t="n">
-        <v>3.624556267058225</v>
+        <v>3.623311282207553</v>
       </c>
       <c r="N5" t="n">
-        <v>24.47704593957765</v>
+        <v>24.45255871865667</v>
       </c>
       <c r="O5" t="n">
-        <v>4.947428214696767</v>
+        <v>4.944952853026677</v>
       </c>
       <c r="P5" t="n">
-        <v>356.8022555247894</v>
+        <v>356.8497608147552</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35336,28 +35519,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2226508087475507</v>
+        <v>0.2183937246198659</v>
       </c>
       <c r="J6" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K6" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07761107967548131</v>
+        <v>0.07549706124589783</v>
       </c>
       <c r="M6" t="n">
-        <v>4.199455551807656</v>
+        <v>4.195612345714809</v>
       </c>
       <c r="N6" t="n">
-        <v>34.21466268276373</v>
+        <v>34.12632083027331</v>
       </c>
       <c r="O6" t="n">
-        <v>5.849330105470517</v>
+        <v>5.841773774314897</v>
       </c>
       <c r="P6" t="n">
-        <v>361.8020274516074</v>
+        <v>361.8463949282263</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35414,28 +35597,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1866666413153683</v>
+        <v>0.1837936390344363</v>
       </c>
       <c r="J7" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K7" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07685908787421492</v>
+        <v>0.07535750668585328</v>
       </c>
       <c r="M7" t="n">
-        <v>3.757720609662248</v>
+        <v>3.748880275486931</v>
       </c>
       <c r="N7" t="n">
-        <v>24.34343008841355</v>
+        <v>24.25684698262784</v>
       </c>
       <c r="O7" t="n">
-        <v>4.933906169396977</v>
+        <v>4.925124057587569</v>
       </c>
       <c r="P7" t="n">
-        <v>369.1013390609417</v>
+        <v>369.1312616634045</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35492,28 +35675,28 @@
         <v>0.0704</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2179760207671295</v>
+        <v>0.2129501780450501</v>
       </c>
       <c r="J8" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K8" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0936413158043895</v>
+        <v>0.09029270893970387</v>
       </c>
       <c r="M8" t="n">
-        <v>3.720051579533564</v>
+        <v>3.721800344451304</v>
       </c>
       <c r="N8" t="n">
-        <v>26.70689439698754</v>
+        <v>26.69536835086384</v>
       </c>
       <c r="O8" t="n">
-        <v>5.167871360336627</v>
+        <v>5.166756076191699</v>
       </c>
       <c r="P8" t="n">
-        <v>365.497865559073</v>
+        <v>365.5502442398357</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35570,28 +35753,28 @@
         <v>0.0829</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2198322420783191</v>
+        <v>0.2157374954748122</v>
       </c>
       <c r="J9" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K9" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1283000847830036</v>
+        <v>0.1249077061679473</v>
       </c>
       <c r="M9" t="n">
-        <v>3.283462638196945</v>
+        <v>3.286283785386879</v>
       </c>
       <c r="N9" t="n">
-        <v>19.06760713596264</v>
+        <v>19.05227325956756</v>
       </c>
       <c r="O9" t="n">
-        <v>4.366647127483814</v>
+        <v>4.364890979115923</v>
       </c>
       <c r="P9" t="n">
-        <v>367.0162304853699</v>
+        <v>367.0589061952131</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35648,28 +35831,28 @@
         <v>0.0769</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1931477798285965</v>
+        <v>0.1885302000658763</v>
       </c>
       <c r="J10" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K10" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1053431847338748</v>
+        <v>0.1013590277182778</v>
       </c>
       <c r="M10" t="n">
-        <v>3.338343065633705</v>
+        <v>3.346369262368482</v>
       </c>
       <c r="N10" t="n">
-        <v>18.3993647061234</v>
+        <v>18.41266054793419</v>
       </c>
       <c r="O10" t="n">
-        <v>4.289448065441917</v>
+        <v>4.290997616864194</v>
       </c>
       <c r="P10" t="n">
-        <v>375.8392640322446</v>
+        <v>375.8873912880822</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35726,28 +35909,28 @@
         <v>0.0823</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1452614868942237</v>
+        <v>0.1407467976995045</v>
       </c>
       <c r="J11" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K11" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07475260438954268</v>
+        <v>0.07080133026074786</v>
       </c>
       <c r="M11" t="n">
-        <v>2.884021204018507</v>
+        <v>2.893128161133635</v>
       </c>
       <c r="N11" t="n">
-        <v>15.1672159401183</v>
+        <v>15.19060660443753</v>
       </c>
       <c r="O11" t="n">
-        <v>3.894511001411898</v>
+        <v>3.897512874184963</v>
       </c>
       <c r="P11" t="n">
-        <v>383.1055965636505</v>
+        <v>383.1526478704653</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35804,28 +35987,28 @@
         <v>0.0887</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1636617849788841</v>
+        <v>0.1616103713333422</v>
       </c>
       <c r="J12" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K12" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07929697607920561</v>
+        <v>0.07820512111308797</v>
       </c>
       <c r="M12" t="n">
-        <v>3.223009176852836</v>
+        <v>3.216629001975251</v>
       </c>
       <c r="N12" t="n">
-        <v>18.06054562487475</v>
+        <v>17.98740297972867</v>
       </c>
       <c r="O12" t="n">
-        <v>4.249770067294787</v>
+        <v>4.241155854213409</v>
       </c>
       <c r="P12" t="n">
-        <v>381.7824806424682</v>
+        <v>381.8038621295377</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35882,28 +36065,28 @@
         <v>0.075</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1754339828464603</v>
+        <v>0.1725956192574113</v>
       </c>
       <c r="J13" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K13" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07628148978966964</v>
+        <v>0.07466271927313173</v>
       </c>
       <c r="M13" t="n">
-        <v>3.462281835560373</v>
+        <v>3.456136218202928</v>
       </c>
       <c r="N13" t="n">
-        <v>21.67603615424799</v>
+        <v>21.60417848547664</v>
       </c>
       <c r="O13" t="n">
-        <v>4.655753016886527</v>
+        <v>4.648029527173493</v>
       </c>
       <c r="P13" t="n">
-        <v>383.9573140687193</v>
+        <v>383.9868793702647</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35960,28 +36143,28 @@
         <v>0.0617</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2798536406069263</v>
+        <v>0.2778314665515385</v>
       </c>
       <c r="J14" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K14" t="n">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1711963923231262</v>
+        <v>0.1706081243344456</v>
       </c>
       <c r="M14" t="n">
-        <v>3.472300057000643</v>
+        <v>3.464814124318366</v>
       </c>
       <c r="N14" t="n">
-        <v>22.0240337169985</v>
+        <v>21.93060812348214</v>
       </c>
       <c r="O14" t="n">
-        <v>4.692977063336076</v>
+        <v>4.683012718697456</v>
       </c>
       <c r="P14" t="n">
-        <v>383.6155662050612</v>
+        <v>383.6366461167191</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36019,7 +36202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O561"/>
+  <dimension ref="A1:O564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79207,6 +79390,237 @@
         </is>
       </c>
     </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-35.02876710287373,173.9163915747402</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-35.0292882313928,173.9157407610642</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-35.02990120106594,173.91523785054295</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>-35.03055460213862,173.91480809161644</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>-35.03122733628092,173.91443605672424</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>-35.03191511166942,173.91415515587323</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>-35.03262208412603,173.91393484703337</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>-35.033348382268166,173.91378280889248</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>-35.03408041459707,173.91365127959824</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>-35.0347966699003,173.91349224755916</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>-35.0355168234696,173.91338943587795</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>-35.036234849206465,173.9132901637662</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>-35.036958216674485,173.9133048984145</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-35.02875415534496,173.916370086338</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>-35.02928812482812,173.91574058420434</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-35.02989113474842,173.9152204589317</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>-35.0305514888125,173.9148016700301</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>-35.03122213851205,173.9144225540104</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>-35.03191345638783,173.91414854951</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>-35.03261965380785,173.913919563821</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>-35.033346293393684,173.91377124529083</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>-35.03407632165454,173.913630828654</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>-35.03479542926448,173.91348427684065</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>-35.03551522564779,173.91337443286722</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>-35.03623413828929,173.91327670749658</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>-35.03695823576655,173.91330873528906</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:47+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-35.028757032573914,173.9163748615379</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>-35.02928908391017,173.9157421759431</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>-35.029894196154544,173.9152257481326</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>-35.03055496841227,173.9148088470972</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>-35.031227183405385,173.91443565958556</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>-35.03191679322496,173.91416186709964</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>-35.03262240930929,173.91393689197028</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>-35.03334822753676,173.91378195232937</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>-35.034078666569954,173.91364254534056</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>-35.03479703873788,173.91349461723232</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>-35.035516279284124,173.91338432615683</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>-35.03623516131597,173.91329607139684</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>-35.03695831704281,173.9133250694121</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
